--- a/docs/downloads/经营分_鲁西省区__聊宁片区_2026-10-18.xlsx
+++ b/docs/downloads/经营分_鲁西省区__聊宁片区_2026-10-18.xlsx
@@ -801,7 +801,7 @@
         <v>75</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -1065,7 +1065,7 @@
         <v>87</v>
       </c>
       <c r="I6" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -1126,22 +1126,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>聊城市</t>
+          <t>济宁市</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>7220335520839944195</t>
+          <t>7587227362815641643</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>希岸·轻雅酒店聊城阳谷新世界广场店</t>
+          <t>潮漫酒店(济宁汶上宝相寺店)</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>希岸·轻雅酒店(聊城阳谷新世界广场店)</t>
+          <t>潮漫酒店(济宁汶上宝相寺店)</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1153,7 +1153,7 @@
         <v>90</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -1167,13 +1167,13 @@
         <v>10</v>
       </c>
       <c r="M7" t="n">
+        <v>20</v>
+      </c>
+      <c r="N7" t="n">
+        <v>30</v>
+      </c>
+      <c r="O7" t="n">
         <v>25</v>
-      </c>
-      <c r="N7" t="n">
-        <v>30</v>
-      </c>
-      <c r="O7" t="n">
-        <v>20</v>
       </c>
       <c r="P7" t="n">
         <v>30</v>
@@ -1214,34 +1214,34 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>济宁市</t>
+          <t>聊城市</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>7587227362815641643</t>
+          <t>7220335520839944195</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>潮漫酒店(济宁汶上宝相寺店)</t>
+          <t>希岸·轻雅酒店聊城阳谷新世界广场店</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>潮漫酒店(济宁汶上宝相寺店)</t>
+          <t>希岸·轻雅酒店(聊城阳谷新世界广场店)</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>未认证</t>
+          <t>已认证</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="I8" t="n">
-        <v>-5</v>
+        <v>5</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -1255,7 +1255,7 @@
         <v>10</v>
       </c>
       <c r="M8" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="N8" t="n">
         <v>30</v>
@@ -1742,22 +1742,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>济宁市</t>
+          <t>聊城市</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>7255531206723242043</t>
+          <t>6601138302504404996</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>维也纳智好酒店（嘉祥一中得力广场店）</t>
+          <t>维也纳酒店（聊城大学湖南路店）</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>维也纳智好酒店(嘉祥一中得力广场店)</t>
+          <t>维也纳酒店(聊城大学湖南路店)</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1769,7 +1769,7 @@
         <v>100</v>
       </c>
       <c r="I14" t="n">
-        <v>-5</v>
+        <v>-10</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -1835,17 +1835,17 @@
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>6601138302504404996</t>
+          <t>6867283925773977613</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>维也纳酒店（聊城大学湖南路店）</t>
+          <t>维也纳酒店（聊城高新区月季公园店）</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>维也纳酒店(聊城大学湖南路店)</t>
+          <t>维也纳酒店(聊城高新区月季公园店)</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1857,11 +1857,11 @@
         <v>100</v>
       </c>
       <c r="I15" t="n">
-        <v>-15</v>
+        <v>0</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>稳房源,拿收益</t>
+          <t>提质量,拿收益</t>
         </is>
       </c>
       <c r="K15" t="n">
@@ -1871,19 +1871,19 @@
         <v>10</v>
       </c>
       <c r="M15" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="N15" t="n">
         <v>30</v>
       </c>
       <c r="O15" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="P15" t="n">
         <v>30</v>
       </c>
       <c r="Q15" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="R15" t="n">
         <v>30</v>
@@ -1918,22 +1918,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>聊城市</t>
+          <t>济宁市</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>6867283925773977613</t>
+          <t>7235892487225608192</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>维也纳酒店（聊城高新区月季公园店）</t>
+          <t>麗枫酒店（济宁嘉祥高铁站汽车总站店）</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>维也纳酒店(聊城高新区月季公园店)</t>
+          <t>麗枫酒店(济宁嘉祥高铁站汽车总站店)</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1949,7 +1949,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>提质量,拿收益</t>
+          <t>稳房源,提质量,拿收益</t>
         </is>
       </c>
       <c r="K16" t="n">
@@ -1959,13 +1959,13 @@
         <v>10</v>
       </c>
       <c r="M16" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="N16" t="n">
         <v>30</v>
       </c>
       <c r="O16" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="P16" t="n">
         <v>30</v>
@@ -2011,17 +2011,17 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>7235892487225608192</t>
+          <t>7398469779898271779</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>麗枫酒店（济宁嘉祥高铁站汽车总站店）</t>
+          <t>IU酒店（济宁嘉祥兖兰路火车站店）</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>麗枫酒店(济宁嘉祥高铁站汽车总站店)</t>
+          <t>IU酒店(嘉祥兖兰路火车站店)</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -2030,14 +2030,14 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>稳房源,提质量,拿收益</t>
+          <t>稳房源,拿收益</t>
         </is>
       </c>
       <c r="K17" t="n">
@@ -2047,19 +2047,19 @@
         <v>10</v>
       </c>
       <c r="M17" t="n">
+        <v>20</v>
+      </c>
+      <c r="N17" t="n">
+        <v>30</v>
+      </c>
+      <c r="O17" t="n">
+        <v>30</v>
+      </c>
+      <c r="P17" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q17" t="n">
         <v>25</v>
-      </c>
-      <c r="N17" t="n">
-        <v>30</v>
-      </c>
-      <c r="O17" t="n">
-        <v>25</v>
-      </c>
-      <c r="P17" t="n">
-        <v>30</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>20</v>
       </c>
       <c r="R17" t="n">
         <v>30</v>
@@ -2094,22 +2094,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>济宁市</t>
+          <t>聊城市</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>7398469779898271779</t>
+          <t>6601178255955331085</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>IU酒店（济宁嘉祥兖兰路火车站店）</t>
+          <t>维也纳国际酒店（聊城开发区钢管城店）</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>IU酒店(嘉祥兖兰路火车站店)</t>
+          <t>维也纳国际酒店(聊城开发区钢管城店)</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -2121,11 +2121,11 @@
         <v>105</v>
       </c>
       <c r="I18" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>稳房源,拿收益</t>
+          <t>拿收益</t>
         </is>
       </c>
       <c r="K18" t="n">
@@ -2135,7 +2135,7 @@
         <v>10</v>
       </c>
       <c r="M18" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="N18" t="n">
         <v>30</v>
@@ -2147,7 +2147,7 @@
         <v>30</v>
       </c>
       <c r="Q18" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="R18" t="n">
         <v>30</v>
@@ -2182,22 +2182,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>聊城市</t>
+          <t>济宁市</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>6601178255955331085</t>
+          <t>7255531206723242043</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>维也纳国际酒店（聊城开发区钢管城店）</t>
+          <t>维也纳智好酒店（嘉祥一中得力广场店）</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>维也纳国际酒店(聊城开发区钢管城店)</t>
+          <t>维也纳智好酒店(嘉祥一中得力广场店)</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -2213,7 +2213,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>拿收益</t>
+          <t>稳房源,拿收益</t>
         </is>
       </c>
       <c r="K19" t="n">
@@ -2223,7 +2223,7 @@
         <v>10</v>
       </c>
       <c r="M19" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="N19" t="n">
         <v>30</v>
@@ -2235,7 +2235,7 @@
         <v>30</v>
       </c>
       <c r="Q19" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="R19" t="n">
         <v>30</v>
@@ -2561,7 +2561,7 @@
         <v>110</v>
       </c>
       <c r="I23" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -2825,7 +2825,7 @@
         <v>110</v>
       </c>
       <c r="I26" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
@@ -2994,7 +2994,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>未认证</t>
+          <t>已认证</t>
         </is>
       </c>
       <c r="H28" t="n">
@@ -3793,7 +3793,7 @@
         <v>115</v>
       </c>
       <c r="I37" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
@@ -3969,7 +3969,7 @@
         <v>115</v>
       </c>
       <c r="I39" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
